--- a/rules/CORE-000777/negative/01/data/unit-test-coreid-CG0502-negative.xlsx
+++ b/rules/CORE-000777/negative/01/data/unit-test-coreid-CG0502-negative.xlsx
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,6 +572,62 @@
       <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mh.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>$RELMIDS_EXISTS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mh.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
         </is>
       </c>
     </row>
@@ -632,7 +688,7 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>MIDS</t>
+          <t>RELMIDS</t>
         </is>
       </c>
     </row>
@@ -679,8 +735,7 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Disease Milestone
-Instance Name</t>
+          <t>Relationship to Disease Milestone Instance Name</t>
         </is>
       </c>
     </row>
@@ -757,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -801,7 +856,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>DIAG</t>
+          <t>AT TIME OF</t>
         </is>
       </c>
     </row>
@@ -846,7 +901,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>DIAG</t>
+          <t>AFTER</t>
         </is>
       </c>
     </row>
